--- a/data/gravel/Massi Brunello 2025.xlsx
+++ b/data/gravel/Massi Brunello 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F36FAE-6017-2D4B-8796-A208DEA9F4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C0E0AF-F139-304F-99DA-C9CB6D84CEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4240" yWindow="2620" windowWidth="24560" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -242,9 +242,6 @@
     <t>handlebar</t>
   </si>
   <si>
-    <t>drop bar</t>
-  </si>
-  <si>
     <t>fork</t>
   </si>
   <si>
@@ -342,6 +339,12 @@
   </si>
   <si>
     <t>a8:h30</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>https://masibikes.com/cdn/shop/files/MY23-Masi-Brunello-ADX-Angle-2_bfa3f1db-4e1e-4d83-8df9-c24ab98d2fca.jpg?v=1713721441&amp;width=1346</t>
   </si>
 </sst>
 </file>
@@ -693,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -701,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -725,7 +728,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -733,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -741,25 +749,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
         <v>95</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>96</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>97</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>98</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>99</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>100</v>
-      </c>
-      <c r="H8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -767,7 +775,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>541</v>
@@ -793,7 +801,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10">
         <v>440</v>
@@ -819,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11">
         <v>551</v>
@@ -845,7 +853,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12">
         <v>388</v>
@@ -871,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13">
         <v>733</v>
@@ -897,7 +905,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>114.5</v>
@@ -923,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>71.8</v>
@@ -949,7 +957,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>74.5</v>
@@ -975,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3">
         <v>1011.1</v>
@@ -1001,7 +1009,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="3">
         <v>425</v>
@@ -1027,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19">
         <v>74</v>
@@ -1053,7 +1061,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20">
         <v>45</v>
@@ -1079,7 +1087,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>90</v>
@@ -1105,7 +1113,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <v>400</v>
@@ -1132,7 +1140,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>165</v>
@@ -1288,17 +1296,17 @@
       <c r="A34" t="s">
         <v>68</v>
       </c>
-      <c r="B34" t="s">
-        <v>69</v>
+      <c r="B34" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
         <v>70</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
       </c>
       <c r="H35" s="1"/>
     </row>
@@ -1307,7 +1315,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="3"/>
@@ -1380,7 +1388,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -1401,7 +1409,7 @@
         <v>45</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1434,7 +1442,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1442,7 +1450,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1490,7 +1498,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1528,7 +1536,7 @@
         <v>65</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
